--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -531,13 +531,13 @@
         <v>23.53</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -551,28 +551,28 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>83.87</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
-        <v>16.13</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -589,25 +589,25 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H4" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -624,25 +624,25 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
-        <v>13.64</v>
+        <v>9.09</v>
       </c>
       <c r="I5" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -659,25 +659,25 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>60.47</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>39.53</v>
+        <v>18.6</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -691,28 +691,28 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>66.67</v>
+        <v>90.7</v>
       </c>
       <c r="H7" s="1">
-        <v>33.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -799,25 +799,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H10" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -831,28 +831,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>95.12</v>
+        <v>95</v>
       </c>
       <c r="H11" s="1">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -881,13 +881,13 @@
         <v>2.78</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -956,22 +956,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>29.41</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -985,25 +988,28 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1020,22 +1026,25 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1052,22 +1061,25 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1084,22 +1096,25 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>32.56</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.4</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1113,25 +1128,28 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>13.95</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1212,22 +1230,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>8.82</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1241,25 +1262,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1276,22 +1300,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
   </sheetData>
@@ -1372,13 +1399,13 @@
         <v>23.53</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1392,28 +1419,28 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>83.87</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>16.13</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="2">
         <v>6.8</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1442,13 +1469,13 @@
         <v>15</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1465,25 +1492,25 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>86.36</v>
+        <v>95.45</v>
       </c>
       <c r="H5" s="1">
-        <v>13.64</v>
+        <v>4.55</v>
       </c>
       <c r="I5" s="2">
         <v>7.3</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1500,25 +1527,25 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>60.47</v>
+        <v>67.44</v>
       </c>
       <c r="H6" s="1">
-        <v>39.53</v>
+        <v>32.56</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1532,28 +1559,28 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>66.67</v>
+        <v>86.05</v>
       </c>
       <c r="H7" s="1">
-        <v>33.33</v>
+        <v>13.95</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1655,10 +1682,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1672,28 +1699,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>95.12</v>
+        <v>92.5</v>
       </c>
       <c r="H11" s="1">
-        <v>4.88</v>
+        <v>7.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1710,25 +1737,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>97.22</v>
+        <v>88.89</v>
       </c>
       <c r="H12" s="1">
-        <v>2.78</v>
+        <v>11.11</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -1166,22 +1166,25 @@
         <v>41</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J8">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1609,7 +1612,7 @@
         <v>12.2</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
         <v>5</v>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -968,13 +968,13 @@
         <v>29.41</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1201,22 +1201,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>7.69</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1233,25 +1236,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>91.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H10" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1268,25 +1271,25 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1303,25 +1306,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H12" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1390,16 +1393,16 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="H2" s="1">
-        <v>23.53</v>
+        <v>29.41</v>
       </c>
       <c r="I2" s="2">
         <v>6.9</v>
@@ -1647,7 +1650,7 @@
         <v>7.69</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>3</v>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -776,13 +776,13 @@
         <v>7.69</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1201,25 +1201,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H9" s="1">
-        <v>7.69</v>
+        <v>2.56</v>
       </c>
       <c r="I9" s="2">
         <v>7.8</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1638,25 +1638,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H9" s="1">
-        <v>7.69</v>
+        <v>2.56</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -1650,7 +1650,7 @@
         <v>2.56</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1673,16 +1673,16 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H10" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I10" s="2">
         <v>8.199999999999999</v>
@@ -1708,19 +1708,19 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H11" s="1">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1743,19 +1743,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -1393,19 +1393,19 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H2" s="1">
-        <v>29.41</v>
+        <v>5.88</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1428,19 +1428,19 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="H3" s="1">
-        <v>16.67</v>
+        <v>6.67</v>
       </c>
       <c r="I3" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1463,16 +1463,16 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H4" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I4" s="2">
         <v>7</v>
@@ -1568,16 +1568,16 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H7" s="1">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7" s="2">
         <v>6.8</v>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -1498,16 +1498,16 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H5" s="1">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="I5" s="2">
         <v>7.3</v>
@@ -1533,19 +1533,19 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>67.44</v>
+        <v>90.7</v>
       </c>
       <c r="H6" s="1">
-        <v>32.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20221.xlsx
@@ -729,25 +729,25 @@
         <v>41</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H8" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1166,25 +1166,25 @@
         <v>41</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H8" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
       <c r="I8" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1603,25 +1603,25 @@
         <v>41</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H8" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
       <c r="I8" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
